--- a/ROSA_vitaSPEC/Data/Analyses_chimiques_4var_en_plus.xlsx
+++ b/ROSA_vitaSPEC/Data/Analyses_chimiques_4var_en_plus.xlsx
@@ -60,12 +60,6 @@
     <t>X9.cis.beta.carotene</t>
   </si>
   <si>
-    <t>total.beta.carotenes</t>
-  </si>
-  <si>
-    <t>total.carotenes</t>
-  </si>
-  <si>
     <t>M1</t>
   </si>
   <si>
@@ -984,22 +978,28 @@
     <t>M99</t>
   </si>
   <si>
-    <t>trans.alpha.carotenes</t>
-  </si>
-  <si>
-    <t>trans.beta.carotenes</t>
-  </si>
-  <si>
     <t>ratio.alpha.beta</t>
   </si>
   <si>
     <t>ratio.alpha.natif</t>
   </si>
   <si>
-    <t>total.trans.carotenes.natif</t>
-  </si>
-  <si>
     <t>ratio.beta.natif</t>
+  </si>
+  <si>
+    <t>trans.alpha.carotene</t>
+  </si>
+  <si>
+    <t>trans.beta.carotene</t>
+  </si>
+  <si>
+    <t>total.trans.carotene.natif</t>
+  </si>
+  <si>
+    <t>total.beta.carotene</t>
+  </si>
+  <si>
+    <t>total.carotene</t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1355,7 @@
   <dimension ref="A1:U307"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="12" max="12" width="17.5703125" customWidth="1"/>
+    <col min="12" max="12" width="27.140625" customWidth="1"/>
     <col min="13" max="17" width="27.42578125" customWidth="1"/>
     <col min="18" max="18" width="24" customWidth="1"/>
     <col min="19" max="19" width="19.7109375" customWidth="1"/>
@@ -1398,22 +1398,22 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>11</v>
@@ -1422,15 +1422,15 @@
         <v>12</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>13</v>
+        <v>325</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>14</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>64</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>23</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>24</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>33</v>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>17</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>25</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>31</v>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>24</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>21</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>30</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>37</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>22</v>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>22</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>21</v>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>20</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>18</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>23</v>
@@ -2087,7 +2087,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B19">
         <v>26</v>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B20">
         <v>23</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>19</v>
@@ -2204,7 +2204,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B23">
         <v>17</v>
@@ -2297,7 +2297,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B24">
         <v>20</v>
@@ -2321,7 +2321,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B25">
         <v>29</v>
@@ -2345,7 +2345,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B27">
         <v>36</v>
@@ -2483,7 +2483,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B28">
         <v>18</v>
@@ -2507,7 +2507,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29">
         <v>28</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B30">
         <v>16</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B31">
         <v>35</v>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B32">
         <v>16</v>
@@ -2648,7 +2648,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33">
         <v>20</v>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B34">
         <v>20</v>
@@ -2696,7 +2696,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B35">
         <v>24</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B36">
         <v>19</v>
@@ -2744,7 +2744,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B37">
         <v>29</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B38">
         <v>23</v>
@@ -2792,7 +2792,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B39">
         <v>23</v>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B40">
         <v>26</v>
@@ -2840,7 +2840,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B41">
         <v>21</v>
@@ -2864,7 +2864,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B42">
         <v>19</v>
@@ -2888,7 +2888,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B43">
         <v>36</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B44">
         <v>25</v>
@@ -2981,7 +2981,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B45">
         <v>19</v>
@@ -3050,7 +3050,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B46">
         <v>20</v>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B47">
         <v>19</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B48">
         <v>22</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B49">
         <v>41</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B50">
         <v>26</v>
@@ -3302,7 +3302,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B51">
         <v>27</v>
@@ -3326,7 +3326,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B52">
         <v>33</v>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B53">
         <v>36</v>
@@ -3464,7 +3464,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B54">
         <v>28</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B55">
         <v>29</v>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B56">
         <v>29</v>
@@ -3629,7 +3629,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B57">
         <v>26</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B58">
         <v>25</v>
@@ -3749,7 +3749,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B59">
         <v>27</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B60">
         <v>31</v>
@@ -3866,7 +3866,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B61">
         <v>24</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B62">
         <v>33</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B63">
         <v>32</v>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B64">
         <v>32</v>
@@ -4100,7 +4100,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B65">
         <v>28</v>
@@ -4124,7 +4124,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B66">
         <v>37</v>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B67">
         <v>26</v>
@@ -4262,7 +4262,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B68">
         <v>26</v>
@@ -4331,7 +4331,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B69">
         <v>25</v>
@@ -4355,7 +4355,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B70">
         <v>27</v>
@@ -4379,7 +4379,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B71">
         <v>37</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B72">
         <v>24</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B73">
         <v>41</v>
@@ -4520,7 +4520,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B74">
         <v>37</v>
@@ -4589,7 +4589,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B75">
         <v>49</v>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B76">
         <v>33</v>
@@ -4685,7 +4685,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B77">
         <v>33</v>
@@ -4733,7 +4733,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B78">
         <v>25</v>
@@ -4781,7 +4781,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B79">
         <v>55</v>
@@ -4805,7 +4805,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B80">
         <v>17</v>
@@ -4829,7 +4829,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B81">
         <v>33</v>
@@ -4895,7 +4895,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B82">
         <v>30</v>
@@ -4919,7 +4919,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B83">
         <v>36</v>
@@ -4970,7 +4970,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B84">
         <v>24</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B85">
         <v>38</v>
@@ -5081,7 +5081,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B86">
         <v>41</v>
@@ -5150,7 +5150,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B87">
         <v>41</v>
@@ -5198,7 +5198,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B88">
         <v>34</v>
@@ -5267,7 +5267,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B89">
         <v>63</v>
@@ -5336,7 +5336,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B90">
         <v>53</v>
@@ -5360,7 +5360,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B91">
         <v>28</v>
@@ -5426,7 +5426,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B92">
         <v>35</v>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B93">
         <v>27</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B94">
         <v>34</v>
@@ -5567,7 +5567,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B95">
         <v>37</v>
@@ -5636,7 +5636,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B96">
         <v>56</v>
@@ -5660,7 +5660,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B97">
         <v>23</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B98">
         <v>48</v>
@@ -5732,7 +5732,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B99">
         <v>38</v>
@@ -5756,7 +5756,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B100">
         <v>31</v>
@@ -5804,7 +5804,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B101">
         <v>36</v>
@@ -5828,7 +5828,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B102">
         <v>30</v>
@@ -5852,7 +5852,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B103">
         <v>32</v>
@@ -5921,7 +5921,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B104">
         <v>30</v>
@@ -5945,7 +5945,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B105">
         <v>28</v>
@@ -6014,7 +6014,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B106">
         <v>36</v>
@@ -6083,7 +6083,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B107">
         <v>29</v>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B108">
         <v>34</v>
@@ -6155,7 +6155,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B109">
         <v>76</v>
@@ -6224,7 +6224,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B110">
         <v>35</v>
@@ -6272,7 +6272,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B111">
         <v>57</v>
@@ -6341,7 +6341,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B112">
         <v>36</v>
@@ -6389,7 +6389,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B113">
         <v>44</v>
@@ -6458,7 +6458,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B114">
         <v>25</v>
@@ -6482,7 +6482,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B115">
         <v>26</v>
@@ -6551,7 +6551,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B116">
         <v>37</v>
@@ -6599,7 +6599,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B117">
         <v>47</v>
@@ -6623,7 +6623,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B118">
         <v>28</v>
@@ -6671,7 +6671,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B119">
         <v>34</v>
@@ -6740,7 +6740,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B120">
         <v>34</v>
@@ -6764,7 +6764,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B121">
         <v>42</v>
@@ -6788,7 +6788,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B122">
         <v>38</v>
@@ -6836,7 +6836,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B123">
         <v>32</v>
@@ -6887,7 +6887,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B124">
         <v>29</v>
@@ -6956,7 +6956,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B125">
         <v>23</v>
@@ -6980,7 +6980,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B126">
         <v>53</v>
@@ -7004,7 +7004,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B127">
         <v>37</v>
@@ -7028,7 +7028,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B128">
         <v>25</v>
@@ -7097,7 +7097,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B129">
         <v>32</v>
@@ -7121,7 +7121,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B130">
         <v>41</v>
@@ -7145,7 +7145,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B131">
         <v>41</v>
@@ -7169,7 +7169,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B132">
         <v>25</v>
@@ -7193,7 +7193,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B133">
         <v>25</v>
@@ -7262,7 +7262,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B134">
         <v>72</v>
@@ -7286,7 +7286,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B135">
         <v>20</v>
@@ -7355,7 +7355,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B136">
         <v>29</v>
@@ -7379,7 +7379,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B137">
         <v>23</v>
@@ -7448,7 +7448,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B138">
         <v>43</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B139">
         <v>38</v>
@@ -7496,7 +7496,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B140">
         <v>35</v>
@@ -7565,7 +7565,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B141">
         <v>34</v>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B142">
         <v>27</v>
@@ -7703,7 +7703,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B143">
         <v>33</v>
@@ -7727,7 +7727,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B144">
         <v>25</v>
@@ -7751,7 +7751,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B145">
         <v>26</v>
@@ -7820,7 +7820,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B146">
         <v>17</v>
@@ -7886,7 +7886,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B147">
         <v>20</v>
@@ -7910,7 +7910,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B148">
         <v>25</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B149">
         <v>30</v>
@@ -8000,7 +8000,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B150">
         <v>22</v>
@@ -8066,7 +8066,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B151">
         <v>24</v>
@@ -8090,7 +8090,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B152">
         <v>24</v>
@@ -8138,7 +8138,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B153">
         <v>20</v>
@@ -8186,7 +8186,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B154">
         <v>29</v>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B155">
         <v>23</v>
@@ -8258,7 +8258,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B156">
         <v>23</v>
@@ -8306,7 +8306,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B157">
         <v>23</v>
@@ -8354,7 +8354,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B158">
         <v>20</v>
@@ -8378,7 +8378,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B159">
         <v>22</v>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B160">
         <v>31</v>
@@ -8471,7 +8471,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B161">
         <v>33</v>
@@ -8540,7 +8540,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B162">
         <v>24</v>
@@ -8606,7 +8606,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B163">
         <v>46</v>
@@ -8630,7 +8630,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B164">
         <v>29</v>
@@ -8654,7 +8654,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B165">
         <v>22</v>
@@ -8723,7 +8723,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B166">
         <v>42</v>
@@ -8792,7 +8792,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B167">
         <v>37</v>
@@ -8861,7 +8861,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B168">
         <v>18</v>
@@ -8885,7 +8885,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B169">
         <v>41</v>
@@ -8954,7 +8954,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B170">
         <v>34</v>
@@ -9020,7 +9020,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B171">
         <v>45</v>
@@ -9089,7 +9089,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B172">
         <v>38</v>
@@ -9113,7 +9113,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B173">
         <v>25</v>
@@ -9182,7 +9182,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B174">
         <v>26</v>
@@ -9206,7 +9206,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B175">
         <v>30</v>
@@ -9275,7 +9275,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B176">
         <v>23</v>
@@ -9299,7 +9299,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B177">
         <v>28</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B178">
         <v>38</v>
@@ -9392,7 +9392,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B179">
         <v>26</v>
@@ -9416,7 +9416,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B180">
         <v>21</v>
@@ -9440,7 +9440,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B181">
         <v>33</v>
@@ -9509,7 +9509,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B182">
         <v>33</v>
@@ -9533,7 +9533,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B183">
         <v>23</v>
@@ -9602,7 +9602,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B184">
         <v>30</v>
@@ -9671,7 +9671,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B185">
         <v>25</v>
@@ -9719,7 +9719,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B186">
         <v>31</v>
@@ -9743,7 +9743,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B187">
         <v>30</v>
@@ -9812,7 +9812,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B188">
         <v>23</v>
@@ -9881,7 +9881,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B189">
         <v>20</v>
@@ -9929,7 +9929,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B190">
         <v>47</v>
@@ -9998,7 +9998,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B191">
         <v>18</v>
@@ -10022,7 +10022,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B192">
         <v>26</v>
@@ -10070,7 +10070,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B193">
         <v>32</v>
@@ -10139,7 +10139,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B194">
         <v>20</v>
@@ -10208,7 +10208,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B195">
         <v>44</v>
@@ -10256,7 +10256,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B196">
         <v>25</v>
@@ -10322,7 +10322,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B197">
         <v>36</v>
@@ -10373,7 +10373,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B198">
         <v>44</v>
@@ -10439,7 +10439,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B199">
         <v>26</v>
@@ -10463,7 +10463,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B200">
         <v>34</v>
@@ -10532,7 +10532,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B201">
         <v>32</v>
@@ -10556,7 +10556,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B202">
         <v>23</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B203">
         <v>36</v>
@@ -10649,7 +10649,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B204">
         <v>36</v>
@@ -10673,7 +10673,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B205">
         <v>44</v>
@@ -10742,7 +10742,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B206">
         <v>29</v>
@@ -10790,7 +10790,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B207">
         <v>34</v>
@@ -10838,7 +10838,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B208">
         <v>26</v>
@@ -10904,7 +10904,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B209">
         <v>18</v>
@@ -10952,7 +10952,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B210">
         <v>37</v>
@@ -11000,7 +11000,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B211">
         <v>32</v>
@@ -11048,7 +11048,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B212">
         <v>40</v>
@@ -11099,7 +11099,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B213">
         <v>23</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B214">
         <v>47</v>
@@ -11237,7 +11237,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B215">
         <v>31</v>
@@ -11285,7 +11285,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B216">
         <v>23</v>
@@ -11309,7 +11309,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B217">
         <v>24</v>
@@ -11357,7 +11357,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B218">
         <v>24</v>
@@ -11402,7 +11402,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B219">
         <v>31</v>
@@ -11426,7 +11426,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B220">
         <v>34</v>
@@ -11495,7 +11495,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B221">
         <v>21</v>
@@ -11519,7 +11519,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B222">
         <v>20</v>
@@ -11567,7 +11567,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B223">
         <v>40</v>
@@ -11591,7 +11591,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B224">
         <v>30</v>
@@ -11615,7 +11615,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B225">
         <v>22</v>
@@ -11639,7 +11639,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B226">
         <v>28</v>
@@ -11708,7 +11708,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B227">
         <v>45</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B228">
         <v>39</v>
@@ -11780,7 +11780,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B229">
         <v>47</v>
@@ -11828,7 +11828,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B230">
         <v>24</v>
@@ -11897,7 +11897,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B231">
         <v>26</v>
@@ -11945,7 +11945,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B232">
         <v>39</v>
@@ -11993,7 +11993,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B233">
         <v>20</v>
@@ -12062,7 +12062,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B234">
         <v>20</v>
@@ -12131,7 +12131,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B235">
         <v>24</v>
@@ -12155,7 +12155,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B236">
         <v>21</v>
@@ -12179,7 +12179,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B237">
         <v>20</v>
@@ -12248,7 +12248,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B238">
         <v>25</v>
@@ -12272,7 +12272,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B239">
         <v>21</v>
@@ -12296,7 +12296,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B240">
         <v>14</v>
@@ -12365,7 +12365,7 @@
     </row>
     <row r="241" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B241">
         <v>23</v>
@@ -12389,7 +12389,7 @@
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B242">
         <v>22</v>
@@ -12413,7 +12413,7 @@
     </row>
     <row r="243" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B243">
         <v>19</v>
@@ -12482,7 +12482,7 @@
     </row>
     <row r="244" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B244">
         <v>30</v>
@@ -12506,7 +12506,7 @@
     </row>
     <row r="245" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B245">
         <v>24</v>
@@ -12530,7 +12530,7 @@
     </row>
     <row r="246" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B246">
         <v>20</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="247" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B247">
         <v>37</v>
@@ -12578,7 +12578,7 @@
     </row>
     <row r="248" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B248">
         <v>19</v>
@@ -12647,7 +12647,7 @@
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B249">
         <v>26</v>
@@ -12698,7 +12698,7 @@
     </row>
     <row r="250" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B250">
         <v>68</v>
@@ -12722,7 +12722,7 @@
     </row>
     <row r="251" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B251">
         <v>19</v>
@@ -12788,7 +12788,7 @@
     </row>
     <row r="252" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B252">
         <v>18</v>
@@ -12857,7 +12857,7 @@
     </row>
     <row r="253" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B253">
         <v>28</v>
@@ -12881,7 +12881,7 @@
     </row>
     <row r="254" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B254">
         <v>40</v>
@@ -12905,7 +12905,7 @@
     </row>
     <row r="255" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B255">
         <v>30</v>
@@ -12956,7 +12956,7 @@
     </row>
     <row r="256" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B256">
         <v>22</v>
@@ -12980,7 +12980,7 @@
     </row>
     <row r="257" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B257">
         <v>18</v>
@@ -13004,7 +13004,7 @@
     </row>
     <row r="258" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B258">
         <v>19</v>
@@ -13028,7 +13028,7 @@
     </row>
     <row r="259" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B259">
         <v>31</v>
@@ -13052,7 +13052,7 @@
     </row>
     <row r="260" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B260">
         <v>25</v>
@@ -13076,7 +13076,7 @@
     </row>
     <row r="261" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B261">
         <v>41</v>
@@ -13100,7 +13100,7 @@
     </row>
     <row r="262" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B262">
         <v>34</v>
@@ -13124,7 +13124,7 @@
     </row>
     <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B263">
         <v>20</v>
@@ -13148,7 +13148,7 @@
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B264">
         <v>22</v>
@@ -13217,7 +13217,7 @@
     </row>
     <row r="265" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B265">
         <v>26</v>
@@ -13241,7 +13241,7 @@
     </row>
     <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B266">
         <v>28</v>
@@ -13265,7 +13265,7 @@
     </row>
     <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B267">
         <v>20</v>
@@ -13289,7 +13289,7 @@
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B268">
         <v>19</v>
@@ -13313,7 +13313,7 @@
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B269">
         <v>24</v>
@@ -13337,7 +13337,7 @@
     </row>
     <row r="270" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B270">
         <v>22</v>
@@ -13361,7 +13361,7 @@
     </row>
     <row r="271" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B271">
         <v>43</v>
@@ -13385,7 +13385,7 @@
     </row>
     <row r="272" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B272">
         <v>25</v>
@@ -13409,7 +13409,7 @@
     </row>
     <row r="273" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B273">
         <v>23</v>
@@ -13433,7 +13433,7 @@
     </row>
     <row r="274" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B274">
         <v>20</v>
@@ -13484,7 +13484,7 @@
     </row>
     <row r="275" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B275">
         <v>37</v>
@@ -13553,7 +13553,7 @@
     </row>
     <row r="276" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B276">
         <v>46</v>
@@ -13622,7 +13622,7 @@
     </row>
     <row r="277" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B277">
         <v>26</v>
@@ -13646,7 +13646,7 @@
     </row>
     <row r="278" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B278">
         <v>38</v>
@@ -13715,7 +13715,7 @@
     </row>
     <row r="279" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B279">
         <v>31</v>
@@ -13784,7 +13784,7 @@
     </row>
     <row r="280" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B280">
         <v>26</v>
@@ -13835,7 +13835,7 @@
     </row>
     <row r="281" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B281">
         <v>23</v>
@@ -13859,7 +13859,7 @@
     </row>
     <row r="282" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B282">
         <v>26</v>
@@ -13883,7 +13883,7 @@
     </row>
     <row r="283" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B283">
         <v>24</v>
@@ -13907,7 +13907,7 @@
     </row>
     <row r="284" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B284">
         <v>20</v>
@@ -13931,7 +13931,7 @@
     </row>
     <row r="285" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B285">
         <v>34</v>
@@ -14000,7 +14000,7 @@
     </row>
     <row r="286" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B286">
         <v>28</v>
@@ -14066,7 +14066,7 @@
     </row>
     <row r="287" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B287">
         <v>33</v>
@@ -14090,7 +14090,7 @@
     </row>
     <row r="288" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B288">
         <v>20</v>
@@ -14141,7 +14141,7 @@
     </row>
     <row r="289" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B289">
         <v>35</v>
@@ -14165,7 +14165,7 @@
     </row>
     <row r="290" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B290">
         <v>27</v>
@@ -14189,7 +14189,7 @@
     </row>
     <row r="291" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B291">
         <v>32</v>
@@ -14258,7 +14258,7 @@
     </row>
     <row r="292" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B292">
         <v>30</v>
@@ -14282,7 +14282,7 @@
     </row>
     <row r="293" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B293">
         <v>17</v>
@@ -14306,7 +14306,7 @@
     </row>
     <row r="294" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B294">
         <v>37</v>
@@ -14330,7 +14330,7 @@
     </row>
     <row r="295" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B295">
         <v>21</v>
@@ -14399,7 +14399,7 @@
     </row>
     <row r="296" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B296">
         <v>22</v>
@@ -14423,7 +14423,7 @@
     </row>
     <row r="297" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B297">
         <v>32</v>
@@ -14489,7 +14489,7 @@
     </row>
     <row r="298" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B298">
         <v>24</v>
@@ -14513,7 +14513,7 @@
     </row>
     <row r="299" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B299">
         <v>31</v>
@@ -14582,7 +14582,7 @@
     </row>
     <row r="300" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B300">
         <v>31</v>
@@ -14606,7 +14606,7 @@
     </row>
     <row r="301" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B301">
         <v>21</v>
@@ -14630,7 +14630,7 @@
     </row>
     <row r="302" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B302">
         <v>52</v>
@@ -14654,7 +14654,7 @@
     </row>
     <row r="303" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B303">
         <v>22</v>
@@ -14678,7 +14678,7 @@
     </row>
     <row r="304" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B304">
         <v>25</v>
@@ -14726,7 +14726,7 @@
     </row>
     <row r="305" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B305">
         <v>21</v>
@@ -14795,7 +14795,7 @@
     </row>
     <row r="306" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B306">
         <v>27</v>
@@ -14819,7 +14819,7 @@
     </row>
     <row r="307" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B307">
         <v>29</v>
